--- a/excel/output_stats_sfvv/floyd-warshall/EfficiencyStats.xlsx
+++ b/excel/output_stats_sfvv/floyd-warshall/EfficiencyStats.xlsx
@@ -490,28 +490,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>41.3974</v>
+        <v>42.0503</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>41.3974</v>
+        <v>42.0503</v>
       </c>
       <c r="F2" t="n">
-        <v>353.76</v>
+        <v>360.62</v>
       </c>
       <c r="G2" t="n">
-        <v>356.26</v>
+        <v>371.4</v>
       </c>
       <c r="H2" t="n">
-        <v>351.215</v>
+        <v>332.508</v>
       </c>
       <c r="I2" t="n">
-        <v>351.445</v>
+        <v>333.229</v>
       </c>
       <c r="J2" t="n">
-        <v>108753000</v>
+        <v>53270600000</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
